--- a/backend/files/pizza-nani.xlsx
+++ b/backend/files/pizza-nani.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASMMY\Desktop\labanon_ai\nodi_ai\backend\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0AECC01-7046-4D37-8467-F023940B6F2C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC3463C-D7CE-4599-BDDB-822966157435}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="8130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
   <si>
     <t>name</t>
   </si>
@@ -536,9 +536,15 @@
       <c r="D3" s="5" t="s">
         <v>9</v>
       </c>
+      <c r="F3" s="5" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576" xr:uid="{7A946F35-7583-446E-8D02-010A64C2EBA9}">
+      <formula1>"Add_Ingredient,Remove_Ingredient,Add_Side,Add_Drink,Spice_Level,Cooking_Preference,Size,Add_Sauce,Remove_Sauce,Extra_Protein,Special_Instructions"</formula1>
+    </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{1308C102-F61B-4BC1-A141-FB14143527E9}">
       <formula1>COUNTIF($A:$A,A2)=1</formula1>
     </dataValidation>
